--- a/dcf/AVGO.xlsx
+++ b/dcf/AVGO.xlsx
@@ -859,7 +859,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1141,25 +1141,25 @@
         <v>13</v>
       </c>
       <c r="B5" s="54" t="n">
-        <v>150.3439120340328</v>
+        <v>126.9621518033029</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>144.3171921342257</v>
+        <v>121.915667941302</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>138.5663921684126</v>
+        <v>117.0987748967746</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>133.0773507834835</v>
+        <v>112.4997209610291</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>127.8367012847976</v>
+        <v>108.1074129559652</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>122.8318234860122</v>
+        <v>103.9113763638168</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>118.0507986840223</v>
+        <v>99.90171804333562</v>
       </c>
     </row>
     <row r="6">
@@ -1167,25 +1167,25 @@
         <v>14</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>158.3301894458573</v>
+        <v>133.5626205149439</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>151.9463820915731</v>
+        <v>128.2210123479563</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>145.8559791830689</v>
+        <v>123.1234455324058</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>140.0438895754338</v>
+        <v>118.2573999087475</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>134.4958701099876</v>
+        <v>113.6110579221574</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>129.1984741847623</v>
+        <v>109.1732620419712</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>124.1390036652096</v>
+        <v>104.9334749453543</v>
       </c>
     </row>
     <row r="7">
@@ -1193,25 +1193,25 @@
         <v>15</v>
       </c>
       <c r="B7" s="54" t="n">
-        <v>166.3164668576819</v>
+        <v>140.163089226585</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>159.5755720489205</v>
+        <v>134.5263567546106</v>
       </c>
       <c r="D7" s="54" t="n">
-        <v>153.1455661977252</v>
+        <v>129.148116168037</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>147.0104283673841</v>
+        <v>124.015078856466</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>141.1550389351776</v>
+        <v>119.1147028883495</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>135.5651248835124</v>
+        <v>114.4351477201257</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>130.2272086463969</v>
+        <v>109.965231847373</v>
       </c>
     </row>
     <row r="8">
@@ -1219,25 +1219,25 @@
         <v>16</v>
       </c>
       <c r="B8" s="54" t="n">
-        <v>174.3027442695063</v>
+        <v>146.763557938226</v>
       </c>
       <c r="C8" s="54" t="n">
-        <v>167.2047620062678</v>
+        <v>140.831701161265</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>160.4351532123816</v>
+        <v>135.1727868036682</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>153.9769671593344</v>
+        <v>129.7727578041844</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>147.8142077603677</v>
+        <v>124.6183478545417</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>141.9317755822625</v>
+        <v>119.6970333982801</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>136.3154136275843</v>
+        <v>114.9969887493918</v>
       </c>
     </row>
     <row r="9">
@@ -1245,25 +1245,25 @@
         <v>17</v>
       </c>
       <c r="B9" s="54" t="n">
-        <v>182.2890216813309</v>
+        <v>153.3640266498671</v>
       </c>
       <c r="C9" s="54" t="n">
-        <v>174.8339519636152</v>
+        <v>147.1370455679192</v>
       </c>
       <c r="D9" s="54" t="n">
-        <v>167.7247402270379</v>
+        <v>141.1974574392994</v>
       </c>
       <c r="E9" s="54" t="n">
-        <v>160.9435059512846</v>
+        <v>135.5304367519028</v>
       </c>
       <c r="F9" s="54" t="n">
-        <v>154.4733765855577</v>
+        <v>130.1219928207339</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>148.2984262810126</v>
+        <v>124.9589190764345</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>142.4036186087716</v>
+        <v>120.0287456514104</v>
       </c>
     </row>
     <row r="10">
@@ -1271,25 +1271,25 @@
         <v>18</v>
       </c>
       <c r="B10" s="54" t="n">
-        <v>190.2752990931554</v>
+        <v>159.9644953615081</v>
       </c>
       <c r="C10" s="54" t="n">
-        <v>182.4631419209626</v>
+        <v>153.4423899745736</v>
       </c>
       <c r="D10" s="54" t="n">
-        <v>175.0143272416942</v>
+        <v>147.2221280749306</v>
       </c>
       <c r="E10" s="54" t="n">
-        <v>167.9100447432349</v>
+        <v>141.2881156996213</v>
       </c>
       <c r="F10" s="54" t="n">
-        <v>161.1325454107477</v>
+        <v>135.6256377869261</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>154.6650769797627</v>
+        <v>130.2208047545889</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>148.4918235899589</v>
+        <v>125.0605025534292</v>
       </c>
     </row>
     <row r="11">
@@ -1297,25 +1297,25 @@
         <v>19</v>
       </c>
       <c r="B11" s="54" t="n">
-        <v>198.26157650498</v>
+        <v>166.5649640731492</v>
       </c>
       <c r="C11" s="54" t="n">
-        <v>190.0923318783099</v>
+        <v>159.7477343812279</v>
       </c>
       <c r="D11" s="54" t="n">
-        <v>182.3039142563506</v>
+        <v>153.2467987105618</v>
       </c>
       <c r="E11" s="54" t="n">
-        <v>174.8765835351851</v>
+        <v>147.0457946473397</v>
       </c>
       <c r="F11" s="54" t="n">
-        <v>167.7917142359378</v>
+        <v>141.1292827531182</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>161.0317276785128</v>
+        <v>135.4826904327433</v>
       </c>
       <c r="H11" s="54" t="n">
-        <v>154.5800285711462</v>
+        <v>130.0922594554479</v>
       </c>
     </row>
     <row r="13">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.8980075647209211</v>
+        <v>0.899833344486656</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24446,7 +24446,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24598,13 +24598,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>153.9769671593344</v>
+        <v>129.7727578041844</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>206.5338338581332</v>
+        <v>170.048082456775</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>113.3708786906095</v>
+        <v>97.84053494124248</v>
       </c>
     </row>
     <row r="59">
